--- a/data/trans_dic/IP25B_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP25B_1_R-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,34; 23,33</t>
+          <t>11,2; 23,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,3; 51,17</t>
+          <t>23,57; 49,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,17; 37,69</t>
+          <t>20,32; 38,19</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,42; 25,95</t>
+          <t>15,63; 25,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,0; 25,34</t>
+          <t>15,34; 24,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,77; 24,32</t>
+          <t>16,68; 23,84</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,51; 62,98</t>
+          <t>25,5; 64,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,67; 36,9</t>
+          <t>22,81; 37,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,74; 49,93</t>
+          <t>26,49; 48,65</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,8; 25,19</t>
+          <t>14,8; 24,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,24; 23,86</t>
+          <t>13,07; 23,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,35; 22,89</t>
+          <t>15,33; 22,62</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,3; 35,17</t>
+          <t>20,23; 35,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,71; 28,44</t>
+          <t>20,88; 28,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,7; 29,93</t>
+          <t>21,82; 29,72</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13001; 26736</t>
+          <t>12835; 27073</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34124; 71856</t>
+          <t>33092; 69430</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51429; 96110</t>
+          <t>51813; 97386</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29199; 49138</t>
+          <t>29587; 48938</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40634; 64331</t>
+          <t>38952; 63348</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74324; 107808</t>
+          <t>73947; 105658</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46978; 115982</t>
+          <t>46953; 118232</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40956; 66664</t>
+          <t>41221; 67516</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97539; 182166</t>
+          <t>96640; 177491</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24116; 41043</t>
+          <t>24104; 40680</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23839; 42957</t>
+          <t>23540; 42819</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52648; 78497</t>
+          <t>52575; 77577</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>132180; 228954</t>
+          <t>131679; 231542</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>156383; 214708</t>
+          <t>157692; 216130</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>305178; 420889</t>
+          <t>306744; 417915</t>
         </is>
       </c>
     </row>
